--- a/sheets/조재수대금교본/검수/대금 시나위.xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위.xlsx
@@ -7641,8 +7641,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ
-ﾉ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -7682,7 +7681,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -7696,13 +7695,13 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -7764,8 +7763,7 @@
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-南
-ﾉ</t>
+南</t>
         </is>
       </c>
       <c r="S5" s="24"/>
@@ -7796,7 +7794,7 @@
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰c</t>
+汰</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -7848,20 +7846,11 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21"/>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21"/>
       <c r="K8" s="24"/>
@@ -7869,11 +7858,7 @@
       <c r="M8" s="24"/>
       <c r="N8" s="21"/>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
       <c r="R8" s="21"/>
       <c r="S8" s="24"/>
@@ -7988,7 +7973,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -8019,17 +8004,9 @@
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="23"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="L13" s="21"/>
       <c r="M13" s="23"/>
       <c r="N13" s="21"/>
       <c r="O13" s="23"/>
@@ -8048,11 +8025,7 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -8060,11 +8033,7 @@
         </is>
       </c>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
@@ -8138,7 +8107,6 @@
       <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-ﾉ
 汰</t>
         </is>
       </c>
@@ -8151,7 +8119,7 @@
       <c r="E17" s="22"/>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕c</t>
+          <t xml:space="preserve">潕</t>
         </is>
       </c>
       <c r="G17" s="22"/>
@@ -8163,7 +8131,7 @@
       <c r="I17" s="22"/>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應c</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="K17" s="22"/>
@@ -8175,8 +8143,7 @@
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ
-ﾉ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="O17" s="22"/>
@@ -8207,11 +8174,7 @@
         </is>
       </c>
       <c r="C18" s="23"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D18" s="21"/>
       <c r="E18" s="23"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
@@ -8221,7 +8184,7 @@
       <c r="G18" s="23"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I18" s="23"/>
@@ -8241,7 +8204,7 @@
       <c r="O18" s="23"/>
       <c r="P18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q18" s="23"/>
@@ -8256,16 +8219,12 @@
       <c r="C19" s="24"/>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㄴ湳淋
+          <t xml:space="preserve">湳淋
 㳞</t>
         </is>
       </c>
       <c r="E19" s="24"/>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F19" s="21"/>
       <c r="G19" s="24"/>
       <c r="H19" s="21"/>
       <c r="I19" s="24"/>
@@ -8275,8 +8234,7 @@
       <c r="M19" s="24"/>
       <c r="N19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ
-ﾉ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="O19" s="24"/>
@@ -8295,22 +8253,14 @@
       <c r="E20" s="22"/>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="G20" s="22"/>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H20" s="21"/>
       <c r="I20" s="22"/>
-      <c r="J20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J20" s="21"/>
       <c r="K20" s="22"/>
       <c r="L20" s="21"/>
       <c r="M20" s="22"/>
@@ -8364,40 +8314,19 @@
       <c r="C22" s="24"/>
       <c r="D22" s="21"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F22" s="21"/>
       <c r="G22" s="24"/>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="H22" s="21"/>
       <c r="I22" s="24"/>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J22" s="21"/>
       <c r="K22" s="24"/>
       <c r="L22" s="21"/>
       <c r="M22" s="24"/>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N22" s="21"/>
       <c r="O22" s="24"/>
       <c r="P22" s="21"/>
       <c r="Q22" s="24"/>
-      <c r="R22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R22" s="21"/>
       <c r="S22" s="24"/>
       <c r="T22" s="21"/>
       <c r="U22" s="24"/>
@@ -8420,15 +8349,15 @@
       <c r="G23" s="22"/>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="I23" s="22"/>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="K23" s="22"/>
@@ -8448,7 +8377,7 @@
       <c r="Q23" s="22"/>
       <c r="R23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞c
+          <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
@@ -8464,7 +8393,7 @@
       <c r="E24" s="23"/>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="G24" s="23"/>
@@ -8505,12 +8434,7 @@
       <c r="C25" s="24"/>
       <c r="D25" s="21"/>
       <c r="E25" s="24"/>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="F25" s="21"/>
       <c r="G25" s="24"/>
       <c r="H25" s="21"/>
       <c r="I25" s="24"/>
@@ -8540,30 +8464,18 @@
       <c r="E26" s="22"/>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="G26" s="22"/>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H26" s="21"/>
       <c r="I26" s="22"/>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J26" s="21"/>
       <c r="K26" s="22"/>
       <c r="L26" s="21"/>
       <c r="M26" s="22"/>
-      <c r="N26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">∧c</t>
-        </is>
-      </c>
+      <c r="N26" s="21"/>
       <c r="O26" s="22"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="22"/>
@@ -8611,60 +8523,25 @@
         </is>
       </c>
       <c r="C28" s="24"/>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="D28" s="21"/>
       <c r="E28" s="24"/>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F28" s="21"/>
       <c r="G28" s="24"/>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H28" s="21"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L28" s="21"/>
       <c r="M28" s="24"/>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N28" s="21"/>
       <c r="O28" s="24"/>
-      <c r="P28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="P28" s="21"/>
       <c r="Q28" s="24"/>
-      <c r="R28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R28" s="21"/>
       <c r="S28" s="24"/>
       <c r="T28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-‹</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="U28" s="24"/>
@@ -8750,17 +8627,12 @@
       <c r="Q32" s="23"/>
       <c r="R32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ﾉ
-–
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="S32" s="23"/>
-      <c r="T32" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T32" s="21"/>
       <c r="U32" s="23"/>
     </row>
     <row r="33" ht="106.4" customHeight="true">
@@ -8844,7 +8716,7 @@
       <c r="T35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ﾉ</t>
+潢</t>
         </is>
       </c>
       <c r="U35" s="23"/>
@@ -8867,11 +8739,7 @@
       <c r="O36" s="24"/>
       <c r="P36" s="21"/>
       <c r="Q36" s="24"/>
-      <c r="R36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R36" s="21"/>
       <c r="S36" s="24"/>
       <c r="T36" s="21" t="inlineStr">
         <is>
@@ -8900,15 +8768,15 @@
       <c r="Q37" s="22"/>
       <c r="R37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="S37" s="22"/>
       <c r="T37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-南ㄴ</t>
+南</t>
         </is>
       </c>
       <c r="U37" s="22"/>
@@ -8958,11 +8826,7 @@
       <c r="O39" s="24"/>
       <c r="P39" s="21"/>
       <c r="Q39" s="24"/>
-      <c r="R39" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R39" s="21"/>
       <c r="S39" s="24"/>
       <c r="T39" s="21"/>
       <c r="U39" s="24"/>
@@ -9039,18 +8903,9 @@
       <c r="O42" s="24"/>
       <c r="P42" s="21"/>
       <c r="Q42" s="24"/>
-      <c r="R42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R42" s="21"/>
       <c r="S42" s="24"/>
-      <c r="T42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="T42" s="21"/>
       <c r="U42" s="24"/>
     </row>
     <row r="43" ht="6.0" customHeight="true">
@@ -9099,8 +8954,7 @@
       <c r="E45" s="22"/>
       <c r="F45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-ﾉ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G45" s="22"/>
@@ -9119,19 +8973,19 @@
       <c r="K45" s="22"/>
       <c r="L45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕c</t>
+          <t xml:space="preserve">潕</t>
         </is>
       </c>
       <c r="M45" s="22"/>
       <c r="N45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="O45" s="22"/>
       <c r="P45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q45" s="22"/>
@@ -9153,7 +9007,7 @@
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C46" s="23"/>
@@ -9212,15 +9066,11 @@
       <c r="M47" s="24"/>
       <c r="N47" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="O47" s="24"/>
-      <c r="P47" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="P47" s="21"/>
       <c r="Q47" s="24"/>
       <c r="R47" s="21"/>
       <c r="S47" s="24"/>
@@ -9241,7 +9091,7 @@
       <c r="K48" s="22"/>
       <c r="L48" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕c</t>
+          <t xml:space="preserve">潕</t>
         </is>
       </c>
       <c r="M48" s="22"/>
@@ -9307,20 +9157,11 @@
     </row>
     <row r="50" ht="106.4" customHeight="true">
       <c r="A50" s="0"/>
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B50" s="21"/>
       <c r="C50" s="24"/>
       <c r="D50" s="21"/>
       <c r="E50" s="24"/>
-      <c r="F50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F50" s="21"/>
       <c r="G50" s="24"/>
       <c r="H50" s="21"/>
       <c r="I50" s="24"/>
@@ -9332,23 +9173,19 @@
         </is>
       </c>
       <c r="M50" s="24"/>
-      <c r="N50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N50" s="21"/>
       <c r="O50" s="24"/>
       <c r="P50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="Q50" s="24"/>
       <c r="R50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="S50" s="24"/>
@@ -9371,16 +9208,15 @@
       <c r="E51" s="22"/>
       <c r="F51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="G51" s="22"/>
       <c r="H51" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢⊏
-ﾉ</t>
+潢</t>
         </is>
       </c>
       <c r="I51" s="22"/>
@@ -9388,14 +9224,14 @@
       <c r="K51" s="22"/>
       <c r="L51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕c</t>
+          <t xml:space="preserve">潕</t>
         </is>
       </c>
       <c r="M51" s="22"/>
       <c r="N51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="O51" s="22"/>
@@ -9459,11 +9295,7 @@
       <c r="C53" s="24"/>
       <c r="D53" s="21"/>
       <c r="E53" s="24"/>
-      <c r="F53" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F53" s="21"/>
       <c r="G53" s="24"/>
       <c r="H53" s="21"/>
       <c r="I53" s="24"/>
@@ -9471,7 +9303,7 @@
       <c r="K53" s="24"/>
       <c r="L53" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕c</t>
+          <t xml:space="preserve">潕</t>
         </is>
       </c>
       <c r="M53" s="24"/>
@@ -9545,8 +9377,8 @@
       <c r="K55" s="23"/>
       <c r="L55" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕c
-潕c</t>
+          <t xml:space="preserve">潕
+潕</t>
         </is>
       </c>
       <c r="M55" s="23"/>
@@ -9573,11 +9405,7 @@
     </row>
     <row r="56" ht="106.4" customHeight="true">
       <c r="A56" s="0"/>
-      <c r="B56" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B56" s="21"/>
       <c r="C56" s="24"/>
       <c r="D56" s="21" t="inlineStr">
         <is>
@@ -9585,18 +9413,9 @@
         </is>
       </c>
       <c r="E56" s="24"/>
-      <c r="F56" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F56" s="21"/>
       <c r="G56" s="24"/>
-      <c r="H56" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="H56" s="21"/>
       <c r="I56" s="24"/>
       <c r="J56" s="21" t="inlineStr">
         <is>
@@ -9606,8 +9425,7 @@
       <c r="K56" s="24"/>
       <c r="L56" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="M56" s="24"/>
@@ -9948,11 +9766,7 @@
         </is>
       </c>
       <c r="S70" s="24"/>
-      <c r="T70" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T70" s="21"/>
       <c r="U70" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/대금 시나위.xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위.xlsx
@@ -7641,7 +7641,8 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ
+ﾉ</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -7681,7 +7682,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -7695,13 +7696,13 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ</t>
         </is>
       </c>
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -7763,7 +7764,8 @@
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-南</t>
+南
+ﾉ</t>
         </is>
       </c>
       <c r="S5" s="24"/>
@@ -7794,7 +7796,7 @@
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+汰c</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -7846,7 +7848,11 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21"/>
       <c r="G8" s="24"/>
@@ -7973,7 +7979,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰c</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -8004,9 +8010,17 @@
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K13" s="23"/>
-      <c r="L13" s="21"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="M13" s="23"/>
       <c r="N13" s="21"/>
       <c r="O13" s="23"/>
@@ -8107,6 +8121,7 @@
       <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
+ﾉ
 汰</t>
         </is>
       </c>
@@ -8119,7 +8134,7 @@
       <c r="E17" s="22"/>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕c</t>
         </is>
       </c>
       <c r="G17" s="22"/>
@@ -8131,7 +8146,7 @@
       <c r="I17" s="22"/>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應</t>
+          <t xml:space="preserve">應c</t>
         </is>
       </c>
       <c r="K17" s="22"/>
@@ -8143,7 +8158,8 @@
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ
+ﾉ</t>
         </is>
       </c>
       <c r="O17" s="22"/>
@@ -8184,7 +8200,7 @@
       <c r="G18" s="23"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ</t>
         </is>
       </c>
       <c r="I18" s="23"/>
@@ -8204,7 +8220,7 @@
       <c r="O18" s="23"/>
       <c r="P18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ</t>
         </is>
       </c>
       <c r="Q18" s="23"/>
@@ -8219,7 +8235,7 @@
       <c r="C19" s="24"/>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋
+          <t xml:space="preserve">ㄴ湳淋
 㳞</t>
         </is>
       </c>
@@ -8234,7 +8250,8 @@
       <c r="M19" s="24"/>
       <c r="N19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ
+ﾉ</t>
         </is>
       </c>
       <c r="O19" s="24"/>
@@ -8253,14 +8270,22 @@
       <c r="E20" s="22"/>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="G20" s="22"/>
-      <c r="H20" s="21"/>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I20" s="22"/>
-      <c r="J20" s="21"/>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K20" s="22"/>
       <c r="L20" s="21"/>
       <c r="M20" s="22"/>
@@ -8316,7 +8341,11 @@
       <c r="E22" s="24"/>
       <c r="F22" s="21"/>
       <c r="G22" s="24"/>
-      <c r="H22" s="21"/>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I22" s="24"/>
       <c r="J22" s="21"/>
       <c r="K22" s="24"/>
@@ -8349,15 +8378,15 @@
       <c r="G23" s="22"/>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="I23" s="22"/>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="K23" s="22"/>
@@ -8377,7 +8406,7 @@
       <c r="Q23" s="22"/>
       <c r="R23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞c
 汰</t>
         </is>
       </c>
@@ -8393,7 +8422,7 @@
       <c r="E24" s="23"/>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ</t>
         </is>
       </c>
       <c r="G24" s="23"/>
@@ -8434,7 +8463,11 @@
       <c r="C25" s="24"/>
       <c r="D25" s="21"/>
       <c r="E25" s="24"/>
-      <c r="F25" s="21"/>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="G25" s="24"/>
       <c r="H25" s="21"/>
       <c r="I25" s="24"/>
@@ -8464,18 +8497,30 @@
       <c r="E26" s="22"/>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="G26" s="22"/>
-      <c r="H26" s="21"/>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I26" s="22"/>
-      <c r="J26" s="21"/>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K26" s="22"/>
       <c r="L26" s="21"/>
       <c r="M26" s="22"/>
-      <c r="N26" s="21"/>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∧c</t>
+        </is>
+      </c>
       <c r="O26" s="22"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="22"/>
@@ -8523,7 +8568,11 @@
         </is>
       </c>
       <c r="C28" s="24"/>
-      <c r="D28" s="21"/>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="E28" s="24"/>
       <c r="F28" s="21"/>
       <c r="G28" s="24"/>
@@ -8535,7 +8584,11 @@
       <c r="M28" s="24"/>
       <c r="N28" s="21"/>
       <c r="O28" s="24"/>
-      <c r="P28" s="21"/>
+      <c r="P28" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="Q28" s="24"/>
       <c r="R28" s="21"/>
       <c r="S28" s="24"/>
@@ -8627,7 +8680,8 @@
       <c r="Q32" s="23"/>
       <c r="R32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">ﾉ
+–
 △</t>
         </is>
       </c>
@@ -8716,7 +8770,7 @@
       <c r="T35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+潢ﾉ</t>
         </is>
       </c>
       <c r="U35" s="23"/>
@@ -8768,15 +8822,15 @@
       <c r="Q37" s="22"/>
       <c r="R37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="S37" s="22"/>
       <c r="T37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-南</t>
+南ㄴ</t>
         </is>
       </c>
       <c r="U37" s="22"/>
@@ -8905,7 +8959,11 @@
       <c r="Q42" s="24"/>
       <c r="R42" s="21"/>
       <c r="S42" s="24"/>
-      <c r="T42" s="21"/>
+      <c r="T42" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="U42" s="24"/>
     </row>
     <row r="43" ht="6.0" customHeight="true">
@@ -8954,7 +9012,8 @@
       <c r="E45" s="22"/>
       <c r="F45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+ﾉ</t>
         </is>
       </c>
       <c r="G45" s="22"/>
@@ -8973,19 +9032,19 @@
       <c r="K45" s="22"/>
       <c r="L45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕c</t>
         </is>
       </c>
       <c r="M45" s="22"/>
       <c r="N45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ</t>
         </is>
       </c>
       <c r="O45" s="22"/>
       <c r="P45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ</t>
         </is>
       </c>
       <c r="Q45" s="22"/>
@@ -9007,7 +9066,7 @@
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄴ</t>
         </is>
       </c>
       <c r="C46" s="23"/>
@@ -9066,11 +9125,15 @@
       <c r="M47" s="24"/>
       <c r="N47" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">∧∼</t>
         </is>
       </c>
       <c r="O47" s="24"/>
-      <c r="P47" s="21"/>
+      <c r="P47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="Q47" s="24"/>
       <c r="R47" s="21"/>
       <c r="S47" s="24"/>
@@ -9091,7 +9154,7 @@
       <c r="K48" s="22"/>
       <c r="L48" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕c</t>
         </is>
       </c>
       <c r="M48" s="22"/>
@@ -9157,7 +9220,11 @@
     </row>
     <row r="50" ht="106.4" customHeight="true">
       <c r="A50" s="0"/>
-      <c r="B50" s="21"/>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C50" s="24"/>
       <c r="D50" s="21"/>
       <c r="E50" s="24"/>
@@ -9177,15 +9244,15 @@
       <c r="O50" s="24"/>
       <c r="P50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="Q50" s="24"/>
       <c r="R50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="S50" s="24"/>
@@ -9208,15 +9275,16 @@
       <c r="E51" s="22"/>
       <c r="F51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="G51" s="22"/>
       <c r="H51" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+潢⊏
+ﾉ</t>
         </is>
       </c>
       <c r="I51" s="22"/>
@@ -9224,14 +9292,14 @@
       <c r="K51" s="22"/>
       <c r="L51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕c</t>
         </is>
       </c>
       <c r="M51" s="22"/>
       <c r="N51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="O51" s="22"/>
@@ -9303,7 +9371,7 @@
       <c r="K53" s="24"/>
       <c r="L53" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕c</t>
         </is>
       </c>
       <c r="M53" s="24"/>
@@ -9377,8 +9445,8 @@
       <c r="K55" s="23"/>
       <c r="L55" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕
-潕</t>
+          <t xml:space="preserve">潕c
+潕c</t>
         </is>
       </c>
       <c r="M55" s="23"/>
@@ -9415,7 +9483,11 @@
       <c r="E56" s="24"/>
       <c r="F56" s="21"/>
       <c r="G56" s="24"/>
-      <c r="H56" s="21"/>
+      <c r="H56" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I56" s="24"/>
       <c r="J56" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/대금 시나위.xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위.xlsx
@@ -7566,32 +7566,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="15.29" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="106.4" customHeight="true">
+    <row r="3" ht="152.99" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="106.4" customHeight="true">
+    <row r="4" ht="152.99" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="106.4" customHeight="true">
+    <row r="5" ht="152.99" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="106.4" customHeight="true">
+    <row r="6" ht="152.99" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -7809,7 +7809,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="106.4" customHeight="true">
+    <row r="7" ht="152.99" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -7844,7 +7844,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="106.4" customHeight="true">
+    <row r="8" ht="152.99" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -7871,7 +7871,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="106.4" customHeight="true">
+    <row r="9" ht="152.99" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -7914,7 +7914,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="106.4" customHeight="true">
+    <row r="10" ht="152.99" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -7941,7 +7941,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="106.4" customHeight="true">
+    <row r="11" ht="152.99" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -7969,7 +7969,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="106.4" customHeight="true">
+    <row r="12" ht="152.99" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -7996,7 +7996,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="106.4" customHeight="true">
+    <row r="13" ht="152.99" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -8031,7 +8031,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="106.4" customHeight="true">
+    <row r="14" ht="152.99" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="71.43" customHeight="true">
+    <row r="16" ht="102.56" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="106.4" customHeight="true">
+    <row r="17" ht="152.99" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="106.4" customHeight="true">
+    <row r="18" ht="152.99" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="106.4" customHeight="true">
+    <row r="19" ht="152.99" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -8262,7 +8262,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="24"/>
     </row>
-    <row r="20" ht="106.4" customHeight="true">
+    <row r="20" ht="152.99" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -8302,7 +8302,7 @@
       <c r="T20" s="21"/>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="106.4" customHeight="true">
+    <row r="21" ht="152.99" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -8333,7 +8333,7 @@
       <c r="T21" s="21"/>
       <c r="U21" s="23"/>
     </row>
-    <row r="22" ht="106.4" customHeight="true">
+    <row r="22" ht="152.99" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -8360,7 +8360,7 @@
       <c r="T22" s="21"/>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="106.4" customHeight="true">
+    <row r="23" ht="152.99" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
       <c r="T23" s="21"/>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="106.4" customHeight="true">
+    <row r="24" ht="152.99" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -8457,7 +8457,7 @@
       <c r="T24" s="21"/>
       <c r="U24" s="23"/>
     </row>
-    <row r="25" ht="106.4" customHeight="true">
+    <row r="25" ht="152.99" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -8489,7 +8489,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="106.4" customHeight="true">
+    <row r="26" ht="152.99" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -8529,7 +8529,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="106.4" customHeight="true">
+    <row r="27" ht="152.99" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -8560,7 +8560,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="106.4" customHeight="true">
+    <row r="28" ht="152.99" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
     <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="71.43" customHeight="true">
+    <row r="30" ht="102.56" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="106.4" customHeight="true">
+    <row r="31" ht="152.99" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="106.4" customHeight="true">
+    <row r="32" ht="152.99" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="23"/>
@@ -8689,7 +8689,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="23"/>
     </row>
-    <row r="33" ht="106.4" customHeight="true">
+    <row r="33" ht="152.99" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="24"/>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="U33" s="24"/>
     </row>
-    <row r="34" ht="106.4" customHeight="true">
+    <row r="34" ht="152.99" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="22"/>
@@ -8743,7 +8743,7 @@
       <c r="T34" s="21"/>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="106.4" customHeight="true">
+    <row r="35" ht="152.99" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="106.4" customHeight="true">
+    <row r="36" ht="152.99" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="U36" s="24"/>
     </row>
-    <row r="37" ht="106.4" customHeight="true">
+    <row r="37" ht="152.99" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21"/>
       <c r="C37" s="22"/>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="U37" s="22"/>
     </row>
-    <row r="38" ht="106.4" customHeight="true">
+    <row r="38" ht="152.99" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21"/>
       <c r="C38" s="23"/>
@@ -8862,7 +8862,7 @@
       <c r="T38" s="21"/>
       <c r="U38" s="23"/>
     </row>
-    <row r="39" ht="106.4" customHeight="true">
+    <row r="39" ht="152.99" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="24"/>
@@ -8885,7 +8885,7 @@
       <c r="T39" s="21"/>
       <c r="U39" s="24"/>
     </row>
-    <row r="40" ht="106.4" customHeight="true">
+    <row r="40" ht="152.99" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21"/>
       <c r="C40" s="22"/>
@@ -8912,7 +8912,7 @@
       <c r="T40" s="21"/>
       <c r="U40" s="22"/>
     </row>
-    <row r="41" ht="106.4" customHeight="true">
+    <row r="41" ht="152.99" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21"/>
       <c r="C41" s="23"/>
@@ -8939,7 +8939,7 @@
       <c r="T41" s="21"/>
       <c r="U41" s="23"/>
     </row>
-    <row r="42" ht="106.4" customHeight="true">
+    <row r="42" ht="152.99" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="24"/>
@@ -8969,7 +8969,7 @@
     <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="71.43" customHeight="true">
+    <row r="44" ht="102.56" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="106.4" customHeight="true">
+    <row r="45" ht="152.99" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="106.4" customHeight="true">
+    <row r="46" ht="152.99" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
       <c r="T46" s="21"/>
       <c r="U46" s="23"/>
     </row>
-    <row r="47" ht="106.4" customHeight="true">
+    <row r="47" ht="152.99" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="24"/>
@@ -9140,7 +9140,7 @@
       <c r="T47" s="21"/>
       <c r="U47" s="24"/>
     </row>
-    <row r="48" ht="106.4" customHeight="true">
+    <row r="48" ht="152.99" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21"/>
       <c r="C48" s="22"/>
@@ -9175,7 +9175,7 @@
       <c r="T48" s="21"/>
       <c r="U48" s="22"/>
     </row>
-    <row r="49" ht="106.4" customHeight="true">
+    <row r="49" ht="152.99" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21"/>
       <c r="C49" s="23"/>
@@ -9218,7 +9218,7 @@
       <c r="T49" s="21"/>
       <c r="U49" s="23"/>
     </row>
-    <row r="50" ht="106.4" customHeight="true">
+    <row r="50" ht="152.99" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
       <c r="T50" s="21"/>
       <c r="U50" s="24"/>
     </row>
-    <row r="51" ht="106.4" customHeight="true">
+    <row r="51" ht="152.99" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
       <c r="T51" s="21"/>
       <c r="U51" s="22"/>
     </row>
-    <row r="52" ht="106.4" customHeight="true">
+    <row r="52" ht="152.99" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21"/>
       <c r="C52" s="23"/>
@@ -9357,7 +9357,7 @@
       <c r="T52" s="21"/>
       <c r="U52" s="23"/>
     </row>
-    <row r="53" ht="106.4" customHeight="true">
+    <row r="53" ht="152.99" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="24"/>
@@ -9384,7 +9384,7 @@
       <c r="T53" s="21"/>
       <c r="U53" s="24"/>
     </row>
-    <row r="54" ht="106.4" customHeight="true">
+    <row r="54" ht="152.99" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21"/>
       <c r="C54" s="22"/>
@@ -9427,7 +9427,7 @@
       <c r="T54" s="21"/>
       <c r="U54" s="22"/>
     </row>
-    <row r="55" ht="106.4" customHeight="true">
+    <row r="55" ht="152.99" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21"/>
       <c r="C55" s="23"/>
@@ -9471,7 +9471,7 @@
       <c r="T55" s="21"/>
       <c r="U55" s="23"/>
     </row>
-    <row r="56" ht="106.4" customHeight="true">
+    <row r="56" ht="152.99" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21"/>
       <c r="C56" s="24"/>
@@ -9517,7 +9517,7 @@
     <row r="57" ht="6.0" customHeight="true">
       <c r="A57" s="0"/>
     </row>
-    <row r="58" ht="71.43" customHeight="true">
+    <row r="58" ht="102.56" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="20" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
       <c r="T58" s="20"/>
       <c r="U58" s="20"/>
     </row>
-    <row r="59" ht="106.4" customHeight="true">
+    <row r="59" ht="152.99" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="21"/>
       <c r="C59" s="22"/>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="U59" s="22"/>
     </row>
-    <row r="60" ht="106.4" customHeight="true">
+    <row r="60" ht="152.99" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="21"/>
       <c r="C60" s="23"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="U60" s="23"/>
     </row>
-    <row r="61" ht="106.4" customHeight="true">
+    <row r="61" ht="152.99" customHeight="true">
       <c r="A61" s="0"/>
       <c r="B61" s="21"/>
       <c r="C61" s="24"/>
@@ -9626,7 +9626,7 @@
       <c r="T61" s="21"/>
       <c r="U61" s="24"/>
     </row>
-    <row r="62" ht="106.4" customHeight="true">
+    <row r="62" ht="152.99" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="21"/>
       <c r="C62" s="22"/>
@@ -9649,7 +9649,7 @@
       <c r="T62" s="21"/>
       <c r="U62" s="22"/>
     </row>
-    <row r="63" ht="106.4" customHeight="true">
+    <row r="63" ht="152.99" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="21"/>
       <c r="C63" s="23"/>
@@ -9672,7 +9672,7 @@
       <c r="T63" s="21"/>
       <c r="U63" s="23"/>
     </row>
-    <row r="64" ht="106.4" customHeight="true">
+    <row r="64" ht="152.99" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="21"/>
       <c r="C64" s="24"/>
@@ -9695,7 +9695,7 @@
       <c r="T64" s="21"/>
       <c r="U64" s="24"/>
     </row>
-    <row r="65" ht="106.4" customHeight="true">
+    <row r="65" ht="152.99" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="21"/>
       <c r="C65" s="22"/>
@@ -9722,7 +9722,7 @@
       <c r="T65" s="21"/>
       <c r="U65" s="22"/>
     </row>
-    <row r="66" ht="106.4" customHeight="true">
+    <row r="66" ht="152.99" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="21"/>
       <c r="C66" s="23"/>
@@ -9745,7 +9745,7 @@
       <c r="T66" s="21"/>
       <c r="U66" s="23"/>
     </row>
-    <row r="67" ht="106.4" customHeight="true">
+    <row r="67" ht="152.99" customHeight="true">
       <c r="A67" s="0"/>
       <c r="B67" s="21"/>
       <c r="C67" s="24"/>
@@ -9768,7 +9768,7 @@
       <c r="T67" s="21"/>
       <c r="U67" s="24"/>
     </row>
-    <row r="68" ht="106.4" customHeight="true">
+    <row r="68" ht="152.99" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="21"/>
       <c r="C68" s="22"/>
@@ -9791,7 +9791,7 @@
       <c r="T68" s="21"/>
       <c r="U68" s="22"/>
     </row>
-    <row r="69" ht="106.4" customHeight="true">
+    <row r="69" ht="152.99" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="21"/>
       <c r="C69" s="23"/>
@@ -9814,7 +9814,7 @@
       <c r="T69" s="21"/>
       <c r="U69" s="23"/>
     </row>
-    <row r="70" ht="106.4" customHeight="true">
+    <row r="70" ht="152.99" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="21"/>
       <c r="C70" s="24"/>
@@ -9851,7 +9851,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
   <rowBreaks count="4" manualBreakCount="4">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
